--- a/光伏配储项目/电价数据/2026/绿能站.xlsx
+++ b/光伏配储项目/电价数据/2026/绿能站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5099</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72296</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56487</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5183099999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45474</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26826</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21637</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07793000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06393</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05265</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03337</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05458</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03904</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.01058</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01451</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08628</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01695</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-8.000000000000001e-05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00361</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14526</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21301</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23618</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21506</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11758</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00252</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00676</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15875</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.01345</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19304</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22431</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.03329</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.1242</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19622</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.00209</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.24072</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.01288</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45855</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52878</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48738</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6156900000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.51578</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.5188700000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.15582</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5922200000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50374</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50637</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.61913</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.57551</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43509</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.34765</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6264500000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43418</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7582899999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.7397999999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.5845</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54632</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52787</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51675</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51187</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52903</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65644</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.75402</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44312</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.17009</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.09097</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04272</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.22054</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.00396</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.03112</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.03970000000000001</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.04101</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.59376</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.02511</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.06126</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.58772</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01409</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.03971</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.04292</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27031</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23375</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23607</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23471</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44214</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.48331</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.71062</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6141799999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7276900000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84978</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.83329</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5990599999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.31139</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47421</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44898</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.26532</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.23009</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.22417</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.00219</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.03544</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.01391</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.01982</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.02345</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.01804</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.00086</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.01444</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.01454</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.01667</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.08520999999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.08363</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07346999999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21962</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15235</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.21012</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19713</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24922</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.26585</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.25427</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.22518</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.07035</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28599</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.48347</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.00736</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.50418</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39687</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34414</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47945</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19485</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10842</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11303</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08216</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.24971</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21138</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13408</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21688</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04067</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04172</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06113</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17521</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04359</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.00509</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21258</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.00085</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03263</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.05008</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07804999999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19925</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20225</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.14995</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19393</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14121</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22604</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.2785899999999999</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25849</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25432</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29224</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27334</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27606</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04513</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04267</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04496</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04347</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04548</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04664</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04715</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04802</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04770000000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04693</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04809</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04654999999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04807</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04927</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04653</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04732</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04876</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05157</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14712</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03762</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09889000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66447</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10244</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04264</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04588</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03238000000000001</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04064</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10697</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00111</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04121</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04112</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04352</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04101</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04043</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04324</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04028</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03892</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04368</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04211</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03995</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04263</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04641</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14486</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3378</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32305</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27358</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27374</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17441</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16067</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1733</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14964</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16135</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16074</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23968</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21617</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28349</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.01182</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.09848999999999999</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15728</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.19248</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.27372</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78087</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92003</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9283400000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.9076799999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31994</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9308099999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6389600000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22965</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88988</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.58152</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37449</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57457</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82817</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53076</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.81038</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.8071900000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.88137</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8934</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.52808</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43278</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44474</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48981</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25184</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88009</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55179</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66635</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5494</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51049</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46127</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42951</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42243</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58975</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59687</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60202</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64419</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44745</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86525</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.6727799999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.65695</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.7758400000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.02097</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02751</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.50027</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.5047900000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62466</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.69945</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45186</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.51451</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16475</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20122</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.05318</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24807</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27491</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42796</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24381</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44697</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35794</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13633</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7120700000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8061799999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65122</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59111</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42384</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.01279</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27673</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.27203</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.26217</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.26315</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.26651</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.00021</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.28051</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.26157</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.00153</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.22822</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.11141</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.24336</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.24902</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.10844</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.25652</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48959</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43297</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60894</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4658</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68272</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46678</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4396600000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42568</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32659</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40231</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.03075</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.03833</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23729</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14661</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14932</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15628</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14483</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14244</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14489</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14384</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14552</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14342</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05415</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11484</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11376</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14772</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14786</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44186</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44626</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44551</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35074</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.46019</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47039</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.06995999999999999</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.0008900000000000001</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.25111</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.25132</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.24366</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.01166</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.1852</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.09465000000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.14988</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.01209</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.01238</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.007820000000000001</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.19985</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.21053</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.01321</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.19394</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.18259</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.01153</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.21452</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-0.01252</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.21171</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-0.01305</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.01101</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44845</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46167</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24973</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.5163300000000001</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36065</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.26839</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.24047</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.27045</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03245</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25518</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2116</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07546</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18517</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24511</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27172</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42962</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50807</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7806900000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45375</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.44111</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31073</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.02029</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34454</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.0411</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.74421</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64951</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8793</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48809</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.49033</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4605</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34508</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13651</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19538</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24664</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13127</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.02101</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23802</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.00434</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14518</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.01926</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23559</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23808</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.7229099999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.67067</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.70799</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5863200000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47845</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8684299999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46026</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43062</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49357</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47611</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46749</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42163</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50098</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41856</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40796</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.17519</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.00512</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15504</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04412</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03694</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.02196</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.18407</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10919</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.27086</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03920000000000001</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48626</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50847</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42993</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.63697</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7836900000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.7639400000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.79291</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.89624</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.62061</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5853700000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.00338</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.9147000000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.70647</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.77512</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.5347499999999999</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5355599999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.52874</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.5245299999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44684</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.61053</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.45177</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47566</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.49725</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46872</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.46889</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.44146</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.49286</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.42639</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15909</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03964</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46364</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01467</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18508</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.40374</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36266</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.04725</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23569</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25225</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04186</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.14988</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05951</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04254</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14886</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01269</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.12298</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.04690999999999999</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.04007</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.02774</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.15027</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.02518</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.00826</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.03607</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.00283</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3515</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19087</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18481</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13014</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.14839</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00144</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04369</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13726</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.18976</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27699</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22214</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22273</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22361</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22784</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23801</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26504</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24085</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23222</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25161</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23436</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25289</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24156</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.25904</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24685</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.25981</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27435</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25711</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21597</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21434</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18323</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.07934000000000001</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.04332</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.22966</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.15081</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15276</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15319</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.01713</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21521</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.19905</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16223</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15556</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.12932</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15479</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18644</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.10621</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12122</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.18936</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.15691</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2088</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18053</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.16861</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22038</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.16752</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.21885</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22618</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20841</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21559</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.12819</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.00296</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.16908</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16574</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.005900000000000001</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02814</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18589</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.07865000000000001</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.009550000000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23562</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25348</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.20619</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32632</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10561</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.28075</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25661</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.12339</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24631</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25736</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.19072</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14333</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10754</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3322</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.23962</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26257</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.01419</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25943</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28454</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28315</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26864</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.18001</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26249</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26499</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26802</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26369</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.03646</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.04288</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42888</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.01091</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40632</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.55152</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.48041</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45767</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43152</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>1.08292</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50239</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.48075</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46802</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46851</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21234</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17914</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23592</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26313</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19446</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27875</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46706</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5609299999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.54753</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46245</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55226</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49864</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5335299999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5212100000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.81012</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8521799999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5509700000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5536599999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44505</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37692</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27033</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26692</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26581</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26151</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25385</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24698</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23732</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23606</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25312</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.18932</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21126</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13702</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.00118</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.03407</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01353</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01032</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02264</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23561</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01402</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02197</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03126</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02217</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01679</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02977</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06561</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11897</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13937</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16704</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22268</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18845</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20709</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.24877</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40548</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38091</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.80027</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27487</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26087</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23208</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22598</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19506</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19503</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.1995</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21466</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.01327</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01358</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.01556</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.01618</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03607</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07662999999999999</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.03424</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00492</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01422</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04415</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.00778</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.00842</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.00224</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15509</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.04258</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.0139</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.01001</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.006679999999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.00362</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.01417</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.00983</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.0121</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.05841</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22758</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18013</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23056</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5284</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40881</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.40766</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5121599999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27024</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23022</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18436</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.16986</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14587</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17198</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.15905</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08555</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10239</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04783</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06837</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03698</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03775</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03849</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04501</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05919</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05594</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07051</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11241</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.13768</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08508</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14162</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08763</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04588</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21304</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09345000000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.08963</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18504</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12777</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.13919</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16329</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14399</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.17857</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19731</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.19838</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21111</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25372</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25759</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25909</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42107</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4984</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44405</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41607</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38204</v>
       </c>
     </row>
   </sheetData>
